--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131795815</v>
       </c>
       <c r="B2" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>131796217</v>
       </c>
       <c r="B3" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131795815</v>
       </c>
       <c r="B2" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>131796217</v>
       </c>
       <c r="B3" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131795815</v>
       </c>
       <c r="B2" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>131796217</v>
       </c>
       <c r="B3" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131795815</v>
       </c>
       <c r="B2" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>131796217</v>
       </c>
       <c r="B3" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131795815</v>
       </c>
       <c r="B2" t="n">
-        <v>99054</v>
+        <v>99090</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>131796217</v>
       </c>
       <c r="B3" t="n">
-        <v>99054</v>
+        <v>99090</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131795815</v>
       </c>
       <c r="B2" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>131796217</v>
       </c>
       <c r="B3" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62275-2022 artfynd.xlsx
+++ b/artfynd/A 62275-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131795815</v>
       </c>
       <c r="B2" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>131796217</v>
       </c>
       <c r="B3" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
